--- a/tmp/exports/exposure_测试001_2026-05-31_2026-06-29.xlsx
+++ b/tmp/exports/exposure_测试001_2026-05-31_2026-06-29.xlsx
@@ -1186,7 +1186,7 @@
       <c r="H12" s="4" t="n"/>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>深信服-安服-权星 18291349681</t>
+          <t>深信服-安服-欧彪 17685079275</t>
         </is>
       </c>
       <c r="J12" s="3" t="n"/>
